--- a/引脚分配.xlsx
+++ b/引脚分配.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BiShe\SmartFarm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\BiShe\SmartFarm\Project_demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584094D4-7349-4706-BCBF-064BF883E407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D7D00A-61C9-4DB4-94BE-97A63F4DF90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9250" yWindow="2570" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t>GPIO0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -167,18 +167,6 @@
     <t>GPIO45</t>
   </si>
   <si>
-    <t>IIC-SCL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IIC-SDA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>光照传感器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>光照</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -195,19 +183,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ADC0-CH5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADC0-CH6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>随便选了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>GPIO46</t>
+  </si>
+  <si>
+    <t>GY30光照SCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GY30光照SDA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NH3传感器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H2S传感器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>温湿度DHT11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -230,30 +230,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -268,20 +250,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -563,297 +533,281 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:K51"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.625" customWidth="1"/>
+    <col min="3" max="3" width="11.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="H3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" t="s">
         <v>49</v>
       </c>
-      <c r="I3" t="s">
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="K4" t="s">
         <v>50</v>
       </c>
-      <c r="J3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="K4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="5" t="s">
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="6"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="D5:E6"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
